--- a/00-TrainRnns/tau-6/X-otm/BestModels-otm.xlsx
+++ b/00-TrainRnns/tau-6/X-otm/BestModels-otm.xlsx
@@ -477,7 +477,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>90</v>
+        <v>1328</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -513,146 +513,146 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>344</v>
+        <v>920</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_arch12_r0.01_Ld0.3_Lp0.7_seed8826</t>
+          <t>model_arch37_r0.9_Ld0.5_Lp0.5_seed5014</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[12]</t>
+          <t>[37]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.94209293352434</v>
+        <v>0.9660265792568709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9138768689173973</v>
+        <v>0.9148775125813335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9678205281245585</v>
+        <v>0.9562456676056764</v>
       </c>
       <c r="G3" t="n">
-        <v>0.94209293352434</v>
+        <v>0.9660265792568709</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9138768689173973</v>
+        <v>0.9148775125813335</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9678205281245585</v>
+        <v>0.9562456676056764</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9291526696679216</v>
+        <v>0.9335442725221081</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch7_r0.01_Ld0.3_Lp0.7_seed9180</t>
+          <t>model_arch12_r0.01_Ld0.3_Lp0.7_seed8826</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[7]</t>
+          <t>[12]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9868667232025063</v>
+        <v>0.94209293352434</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8998627225481919</v>
+        <v>0.9138768689173973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9306671979679895</v>
+        <v>0.9678205281245585</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9868667232025063</v>
+        <v>0.94209293352434</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8998627225481919</v>
+        <v>0.9138768689173973</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9306671979679895</v>
+        <v>0.9678205281245585</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9253293548130749</v>
+        <v>0.9291526696679216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>394</v>
+        <v>1454</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_arch14_r0.01_Ld0.5_Lp0.5_seed8826</t>
+          <t>model_arch53_r0.01_Ld0.7_Lp0.3_seed9416</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[14]</t>
+          <t>[53]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9815871978401991</v>
+        <v>0.9605641110071627</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8722039220380762</v>
+        <v>0.908969970800356</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9578912841385464</v>
+        <v>0.9501335223005203</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9815871978401991</v>
+        <v>0.9605641110071627</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8722039220380762</v>
+        <v>0.908969970800356</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9578912841385464</v>
+        <v>0.9501335223005203</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9221006992303394</v>
+        <v>0.9277623093383773</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>244</v>
+        <v>2340</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch9_r0.01_Ld0.5_Lp0.5_seed8826</t>
+          <t>model_arch7_r0.01_Ld0.3_Lp0.7_seed9180</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[9]</t>
+          <t>[7]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9646819721902347</v>
+        <v>0.9868667232025063</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8595876434024261</v>
+        <v>0.8998627225481919</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9758735336150222</v>
+        <v>0.9306671979679895</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9646819721902347</v>
+        <v>0.9868667232025063</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8595876434024261</v>
+        <v>0.8998627225481919</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9758735336150222</v>
+        <v>0.9306671979679895</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9176320908571624</v>
+        <v>0.9253293548130749</v>
       </c>
     </row>
   </sheetData>
